--- a/data/synthetic/messy_joinery/jobs 2026.xlsx
+++ b/data/synthetic/messy_joinery/jobs 2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Materials Ordered </t>
+          <t xml:space="preserve">Site Survey </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>site work started</t>
+          <t>materials ordered</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Snagging</t>
+          <t>Site Work Started</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24/01/2026</t>
+          <t>22/01/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INVOICE SENT</t>
+          <t>SNAGGING</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Payment Received</t>
+          <t>Invoice Sent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -647,17 +647,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J-1022</t>
+          <t>J-1021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quote Sent </t>
+          <t xml:space="preserve">Payment Received </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quote Accepted </t>
+          <t xml:space="preserve">Quote Sent </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>25/01/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -706,12 +706,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Materials Ordered </t>
+          <t xml:space="preserve">Quote Accepted </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>site work started</t>
+          <t>site survey</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Snagging</t>
+          <t>Materials Ordered</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INVOICE SENT</t>
+          <t>SITE WORK STARTED</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Payment Received</t>
+          <t>Snagging</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>28/02/2026</t>
+          <t>15/02/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -836,17 +836,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J-1023</t>
+          <t>J-1022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>QUOTE SENT</t>
+          <t>INVOICE SENT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -863,17 +863,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J-1023</t>
+          <t>J-1022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>QUOTE ACCEPTED</t>
+          <t>PAYMENT RECEIVED</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>materials ordered</t>
+          <t>quote sent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15/02/2026</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>site work started</t>
+          <t>quote accepted</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>snagging</t>
+          <t>site survey</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snagging Revisit </t>
+          <t>materials ordered</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>client to confirm</t>
+          <t>done</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>INVOICE SENT</t>
+          <t>SITE WORK STARTED</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Payment Received </t>
+          <t xml:space="preserve">Snagging </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>18/02/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J-1024</t>
+          <t>J-1023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quote Sent </t>
+          <t xml:space="preserve">Site Work Started </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18/02/2026</t>
+          <t>22/02/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Ciara McCrossan</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,17 +1079,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J-1024</t>
+          <t>J-1023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>QUOTE ACCEPTED</t>
+          <t>INVOICE SENT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1106,17 +1106,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J-1024</t>
+          <t>J-1023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Materials Ordered</t>
+          <t>Payment Received</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>28/02/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>site work started</t>
+          <t>quote sent</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>done</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SNAGGING</t>
+          <t xml:space="preserve">Quote Accepted </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>22/02/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>invoice sent</t>
+          <t xml:space="preserve">Site Survey </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t>done</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Payment Received</t>
+          <t>Materials Ordered</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1234,24 +1234,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>done</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>J-1025</t>
+          <t>J-1024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>QUOTE SENT</t>
+          <t>site work started</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>28/02/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1261,51 +1261,51 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>J-1025</t>
+          <t>J-1024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>QUOTE ACCEPTED</t>
+          <t>Snagging</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>08/03/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Ciara McCrossan</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>sorted</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>J-1025</t>
+          <t>J-1024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Re-measure </t>
+          <t xml:space="preserve">Invoice Sent </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>07/03/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>J-1025</t>
+          <t>J-1024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Materials Ordered </t>
+          <t xml:space="preserve">Payment Received </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Site Work Started </t>
+          <t xml:space="preserve">Quote Sent </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15/03/2026</t>
+          <t>01/03/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>snagging</t>
+          <t>quote accepted</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Invoice Sent</t>
+          <t>Site Survey</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1435,34 +1435,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Payment Received</t>
+          <t xml:space="preserve">Site Survey </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tbc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>J-1026</t>
+          <t>J-1025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>QUOTE SENT</t>
+          <t>MATERIALS ORDERED</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1477,46 +1477,46 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>J-1026</t>
+          <t>J-1025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>QUOTE ACCEPTED</t>
+          <t>site work started</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>J-1026</t>
+          <t>J-1025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>materials ordered</t>
+          <t>snagging</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1531,24 +1531,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>J-1026</t>
+          <t>J-1025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Site Work Started</t>
+          <t>Invoice Sent</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>22/03/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1565,27 +1565,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>J-1026</t>
+          <t>J-1025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SNAGGING</t>
+          <t>Payment Received</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>29/03/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1597,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>INVOICE SENT</t>
+          <t xml:space="preserve">Quote Sent </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>14/03/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>sorted</t>
         </is>
       </c>
     </row>
@@ -1624,39 +1624,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Payment Received </t>
+          <t xml:space="preserve">Quote Accepted </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>done</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>J-1027</t>
+          <t>J-1026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>QUOTE SENT</t>
+          <t>site survey</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1666,46 +1666,46 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t>done</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>J-1027</t>
+          <t>J-1026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>quote accepted</t>
+          <t>materials ordered</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/03/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>done</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>J-1027</t>
+          <t>J-1026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Materials Ordered</t>
+          <t>site work started</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1715,93 +1715,93 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>J-1027</t>
+          <t>J-1026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Site Work Started</t>
+          <t>Snagging</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>sorted</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>J-1027</t>
+          <t>J-1026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Snagging</t>
+          <t>invoice sent</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Ciara McCrossan</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>J-1027</t>
+          <t>J-1026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INVOICE SENT</t>
+          <t>Payment Received</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1813,12 +1813,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Payment Received</t>
+          <t>Quote Sent</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1835,17 +1835,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>J-1028</t>
+          <t>J-1027</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>QUOTE SENT</t>
+          <t>Quote Accepted</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1855,51 +1855,51 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>J-1028</t>
+          <t>J-1027</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>quote accepted</t>
+          <t>SITE SURVEY</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Ciara McCrossan</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>J-1028</t>
+          <t>J-1027</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Materials Ordered </t>
+          <t>materials ordered</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1909,29 +1909,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>J-1028</t>
+          <t>J-1027</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>site work started</t>
+          <t xml:space="preserve">Site Work Started </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1943,22 +1943,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>J-1028</t>
+          <t>J-1027</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>snagging</t>
+          <t>Snagging</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Ciara McCrossan</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1970,17 +1970,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>J-1028</t>
+          <t>J-1027</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SNAGGING REVISIT</t>
+          <t>invoice sent</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1990,24 +1990,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>supplier late</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>J-1028</t>
+          <t>J-1027</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invoice Sent </t>
+          <t>payment received</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2029,17 +2029,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Payment Received</t>
+          <t xml:space="preserve">Quote Sent </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2051,61 +2051,61 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>J-1029</t>
+          <t>J-1028</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>QUOTE SENT</t>
+          <t>quote accepted</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>done</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>J-1029</t>
+          <t>J-1028</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>QUOTE ACCEPTED</t>
+          <t xml:space="preserve">Site Survey </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>J-1029</t>
+          <t>J-1028</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2125,115 +2125,358 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>J-1029</t>
+          <t>J-1028</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Site Work Started </t>
+          <t>SITE WORK STARTED</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>done</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>J-1029</t>
+          <t>J-1028</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SNAGGING</t>
+          <t xml:space="preserve">Snagging </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Ciara McCrossan</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>sorted</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>J-1029</t>
+          <t>J-1028</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>invoice sent</t>
+          <t>SITE WORK STARTED</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>tbc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>J-1028</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>invoice sent</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Paddy Lynch</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>J-1028</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Payment Received</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Ciara McCrossan</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done </t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>J-1029</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>QUOTE SENT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>J-1029</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quote Accepted </t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Ciara McCrossan</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done </t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>J-1029</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SITE SURVEY</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Paddy Lynch</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>J-1029</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MATERIALS ORDERED</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Paddy Lynch</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>J-1029</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Site Work Started</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Paddy Lynch</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>J-1029</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snagging </t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>J-1029</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>INVOICE SENT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>J-1029</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
         <is>
           <t>Payment Received</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Ciara McCrossan</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Done </t>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Paddy Lynch</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>complete</t>
         </is>
       </c>
     </row>

--- a/data/synthetic/messy_joinery/jobs 2026.xlsx
+++ b/data/synthetic/messy_joinery/jobs 2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18/01/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>08/03/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25/01/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25/01/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>14/03/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>15/03/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>29/03/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15/02/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>28/03/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18/02/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>22/02/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>28/02/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22/02/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>28/02/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>07/03/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>14/03/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01/03/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>14/03/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>22/03/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>29/03/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>14/03/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>21/03/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2477,6 +2477,865 @@
       <c r="E76" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>J-1036</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>QUOTE SENT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done </t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>J-1037</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>QUOTE SENT</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>client to confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>J-1038</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>quote sent</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>J-1038</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Quote Accepted</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>supplier late</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>J-1039</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>QUOTE SENT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>J-1039</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>QUOTE ACCEPTED</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>J-1039</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>site survey</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>J-1039</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MATERIALS ORDERED</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>waiting on glass</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>J-1040</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Quote Sent</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done </t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>J-1040</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>quote accepted</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>J-1040</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>site survey</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>J-1040</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Materials Ordered</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>waiting on glass</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>J-1041</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Quote Sent</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>J-1041</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>quote accepted</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done </t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>J-1041</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>site survey</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>J-1041</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>materials ordered</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>J-1041</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Site Work Started</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done </t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>J-1042</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Quote Sent</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Ciara McCrossan</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done </t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>J-1042</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>QUOTE ACCEPTED</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Ciara McCrossan</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>J-1042</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Site Survey</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Ciara McCrossan</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>J-1042</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Materials Ordered </t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Ciara McCrossan</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>J-1042</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Site Work Started </t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Ciara McCrossan</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>J-1042</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SNAGGING</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Ciara McCrossan</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>supplier late</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>J-1043</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>QUOTE SENT</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>J-1043</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>quote accepted</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done </t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>J-1043</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SITE SURVEY</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>J-1043</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>materials ordered</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>J-1043</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Site Work Started </t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>J-1043</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SNAGGING</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>J-1043</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>INVOICE SENT</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>J-1044</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Quote Sent</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>J-1044</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>quote accepted</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>J-1044</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Site Survey </t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>tbc</t>
         </is>
       </c>
     </row>
